--- a/outputs/marketing/auditoria/Personas_Sexo.xlsx
+++ b/outputs/marketing/auditoria/Personas_Sexo.xlsx
@@ -27634,10 +27634,10 @@
         </is>
       </c>
       <c r="K356" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L356" s="2" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="M356" s="2" t="inlineStr">
         <is>
@@ -35310,10 +35310,10 @@
         </is>
       </c>
       <c r="K457" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L457" s="3" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
@@ -45874,10 +45874,10 @@
         </is>
       </c>
       <c r="K596" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L596" s="2" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="M596" s="2" t="inlineStr">
         <is>
@@ -46026,10 +46026,10 @@
         </is>
       </c>
       <c r="K598" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L598" s="2" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="M598" s="2" t="inlineStr">
         <is>
